--- a/public/Hotel Inventory Template test 4.xlsx
+++ b/public/Hotel Inventory Template test 4.xlsx
@@ -1,19 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="ZohoSheetWriter"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <workbookPr defaultThemeVersion="166925"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Rushi\internship manual\project\next_adwait_tour\public\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EBAF7C07-502F-40CE-82FE-5E2866EB9747}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView windowHeight="8192" windowWidth="16384"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Hotel Inventory Table Formattin" r:id="rId1" sheetId="1"/>
+    <sheet name="Hotel Inventory Table Formattin" sheetId="1" r:id="rId1"/>
   </sheets>
-  <extLst/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="40">
   <si>
     <t>State</t>
   </si>
@@ -138,12 +145,11 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
-    <numFmt formatCode="dd/mm/yyyy" numFmtId="164"/>
-    <numFmt formatCode="d-mmm-yy" numFmtId="165"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="d\-mmm\-yy"/>
   </numFmts>
-  <fonts count="3">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -177,32 +183,21 @@
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0">
-      <alignment vertical="bottom"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="164" xfId="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="165" xfId="0">
-      <alignment vertical="bottom"/>
-    </xf>
+  <cellXfs count="6">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" customBuiltin="1"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultPivotStyle="PivotStyleLight16" defaultTableStyle="TableStyleMedium2"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -214,29 +209,326 @@
 </styleSheet>
 </file>
 
+<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+  <a:themeElements>
+    <a:clrScheme name="Office">
+      <a:dk1>
+        <a:sysClr val="windowText" lastClr="000000"/>
+      </a:dk1>
+      <a:lt1>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
+      </a:lt1>
+      <a:dk2>
+        <a:srgbClr val="44546A"/>
+      </a:dk2>
+      <a:lt2>
+        <a:srgbClr val="E7E6E6"/>
+      </a:lt2>
+      <a:accent1>
+        <a:srgbClr val="4472C4"/>
+      </a:accent1>
+      <a:accent2>
+        <a:srgbClr val="ED7D31"/>
+      </a:accent2>
+      <a:accent3>
+        <a:srgbClr val="A5A5A5"/>
+      </a:accent3>
+      <a:accent4>
+        <a:srgbClr val="FFC000"/>
+      </a:accent4>
+      <a:accent5>
+        <a:srgbClr val="5B9BD5"/>
+      </a:accent5>
+      <a:accent6>
+        <a:srgbClr val="70AD47"/>
+      </a:accent6>
+      <a:hlink>
+        <a:srgbClr val="0563C1"/>
+      </a:hlink>
+      <a:folHlink>
+        <a:srgbClr val="954F72"/>
+      </a:folHlink>
+    </a:clrScheme>
+    <a:fontScheme name="Office">
+      <a:majorFont>
+        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="游ゴシック Light"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="等线 Light"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Times New Roman"/>
+        <a:font script="Hebr" typeface="Times New Roman"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="MoolBoran"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Times New Roman"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
+      </a:majorFont>
+      <a:minorFont>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="游ゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="等线"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Arial"/>
+        <a:font script="Hebr" typeface="Arial"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="DaunPenh"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Arial"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
+      </a:minorFont>
+    </a:fontScheme>
+    <a:fmtScheme name="Office">
+      <a:fillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="110000"/>
+                <a:satMod val="105000"/>
+                <a:tint val="67000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="105000"/>
+                <a:satMod val="103000"/>
+                <a:tint val="73000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="105000"/>
+                <a:satMod val="109000"/>
+                <a:tint val="81000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:satMod val="103000"/>
+                <a:lumMod val="102000"/>
+                <a:tint val="94000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:satMod val="110000"/>
+                <a:lumMod val="100000"/>
+                <a:shade val="100000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="99000"/>
+                <a:satMod val="120000"/>
+                <a:shade val="78000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+      </a:fillStyleLst>
+      <a:lnStyleLst>
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+      </a:lnStyleLst>
+      <a:effectStyleLst>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="63000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </a:effectStyle>
+      </a:effectStyleLst>
+      <a:bgFillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:tint val="95000"/>
+            <a:satMod val="170000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="93000"/>
+                <a:satMod val="150000"/>
+                <a:shade val="98000"/>
+                <a:lumMod val="102000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:tint val="98000"/>
+                <a:satMod val="130000"/>
+                <a:shade val="90000"/>
+                <a:lumMod val="103000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="63000"/>
+                <a:satMod val="120000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+      </a:bgFillStyleLst>
+    </a:fmtScheme>
+  </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
+  <a:extLst>
+    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+    </a:ext>
+  </a:extLst>
+</a:theme>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main">
-  <dimension ref="A1:AC22"/>
-  <sheetFormatPr defaultRowHeight="16.0" customHeight="1"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:AH22"/>
+  <sheetFormatPr defaultRowHeight="15.95" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="0.26"/>
-    <col min="2" max="2" width="11.26"/>
-    <col min="3" max="3" width="7.55"/>
-    <col min="4" max="4" width="24.11"/>
-    <col min="5" max="5" width="13.91"/>
-    <col min="6" max="6" width="21.46"/>
-    <col min="7" max="7" width="14.3"/>
-    <col min="8" max="8" width="23.05"/>
-    <col min="9" max="9" width="16.29"/>
-    <col min="10" max="11" width="16.82"/>
-    <col min="12" max="13" width="17.48"/>
-    <col min="14" max="14" width="14.44"/>
-    <col min="15" max="15" width="13.64"/>
-    <col min="16" max="16" width="11.39"/>
-    <col min="17" max="2048" width="12.58"/>
+    <col min="1" max="1" width="0.28515625"/>
+    <col min="2" max="2" width="11.28515625"/>
+    <col min="3" max="3" width="7.5703125"/>
+    <col min="4" max="4" width="24.140625"/>
+    <col min="5" max="5" width="13.85546875"/>
+    <col min="6" max="6" width="21.42578125"/>
+    <col min="7" max="7" width="7.140625" customWidth="1"/>
+    <col min="8" max="8" width="15.7109375" customWidth="1"/>
+    <col min="9" max="10" width="14" customWidth="1"/>
+    <col min="11" max="11" width="16.28515625"/>
+    <col min="12" max="13" width="16.85546875"/>
+    <col min="14" max="14" width="17.42578125"/>
+    <col min="18" max="18" width="17.42578125"/>
+    <col min="19" max="19" width="14.42578125"/>
+    <col min="20" max="20" width="13.5703125"/>
+    <col min="21" max="21" width="11.42578125"/>
+    <col min="22" max="2053" width="12.5703125"/>
   </cols>
   <sheetData>
-    <row r="1" ht="14.0">
+    <row r="1" spans="1:33" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A1" s="1"/>
       <c r="B1" s="1" t="s">
         <v>0</v>
@@ -268,44 +560,47 @@
       <c r="K1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+      <c r="N1" s="1"/>
+      <c r="R1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="S1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="T1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="V1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="W1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="S1" s="1" t="s">
+      <c r="X1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="U1" s="1" t="s">
+      <c r="Z1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="V1" s="1" t="s">
+      <c r="AA1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="W1" s="1" t="s">
+      <c r="AB1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="Y1" s="1" t="s">
+      <c r="AD1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="Z1" s="1" t="s">
+      <c r="AE1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="AA1" s="1" t="s">
+      <c r="AF1" s="1" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="2" ht="14.0">
+    <row r="2" spans="1:33" ht="12.75" x14ac:dyDescent="0.2">
       <c r="B2" s="1" t="s">
         <v>10</v>
       </c>
@@ -316,449 +611,473 @@
         <v>12</v>
       </c>
       <c r="E2" s="1">
-        <v>4.9</v>
+        <v>4.9000000000000004</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>13</v>
       </c>
       <c r="G2" s="1">
-        <v>5.0</v>
-      </c>
-      <c r="I2" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="I2" t="s">
         <v>14</v>
       </c>
-      <c r="J2" s="3">
+      <c r="J2" s="5">
         <v>46023</v>
       </c>
       <c r="K2" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="M2" s="1" t="s">
+      <c r="L2" s="3"/>
+      <c r="M2" s="1"/>
+      <c r="R2" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="N2" s="4">
-        <v>46083.0</v>
-      </c>
-      <c r="O2" s="3">
+      <c r="S2" s="4">
+        <v>46083</v>
+      </c>
+      <c r="T2" s="3">
         <v>46143</v>
       </c>
-      <c r="Q2" s="1" t="s">
+      <c r="V2" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="R2" s="4">
-        <v>46144.0</v>
-      </c>
-      <c r="S2" s="1" t="s">
+      <c r="W2" s="4">
+        <v>46144</v>
+      </c>
+      <c r="X2" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="U2" s="1" t="s">
+      <c r="Z2" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="V2" s="4">
-        <v>46242.0</v>
-      </c>
-      <c r="W2" s="3">
+      <c r="AA2" s="4">
+        <v>46242</v>
+      </c>
+      <c r="AB2" s="3">
         <v>46265</v>
       </c>
-      <c r="Y2" s="1" t="s">
+      <c r="AD2" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="Z2" s="4">
-        <v>46242.0</v>
-      </c>
-      <c r="AA2" s="3">
+      <c r="AE2" s="4">
+        <v>46242</v>
+      </c>
+      <c r="AF2" s="3">
         <v>46265</v>
       </c>
     </row>
-    <row r="3" ht="14.0">
-      <c r="I3" s="1" t="s">
+    <row r="3" spans="1:33" ht="12.75" x14ac:dyDescent="0.2">
+      <c r="L3" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="J3" s="1" t="s">
+      <c r="M3" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="K3" s="1" t="s">
+      <c r="N3" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="L3" s="1" t="s">
+      <c r="O3" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="M3" s="1" t="s">
+      <c r="P3" s="1"/>
+      <c r="Q3" s="1"/>
+      <c r="R3" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="N3" s="1" t="s">
+      <c r="S3" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="O3" s="1" t="s">
+      <c r="T3" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="P3" s="1" t="s">
+      <c r="U3" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="Q3" s="1" t="s">
+      <c r="V3" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="R3" s="1" t="s">
+      <c r="W3" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="S3" s="1" t="s">
+      <c r="X3" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="T3" s="1" t="s">
+      <c r="Y3" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="U3" s="1" t="s">
+      <c r="Z3" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="V3" s="1" t="s">
+      <c r="AA3" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="W3" s="1" t="s">
+      <c r="AB3" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="X3" s="1" t="s">
+      <c r="AC3" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="Y3" s="1" t="s">
+      <c r="AD3" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="Z3" s="1" t="s">
+      <c r="AE3" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="AA3" s="1" t="s">
+      <c r="AF3" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="AB3" s="1" t="s">
+      <c r="AG3" s="1" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="4" ht="14.0">
+    <row r="4" spans="1:33" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A4" s="1"/>
       <c r="H4" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="I4" s="1">
-        <v>12000.0</v>
-      </c>
-      <c r="J4" s="1">
-        <v>14000.0</v>
-      </c>
-      <c r="K4" s="1">
-        <v>16000.0</v>
-      </c>
+      <c r="I4" s="1"/>
+      <c r="J4" s="1"/>
       <c r="L4" s="1">
-        <v>14000.0</v>
+        <v>12000</v>
       </c>
       <c r="M4" s="1">
-        <v>12000.0</v>
+        <v>14000</v>
       </c>
       <c r="N4" s="1">
-        <v>14000.0</v>
+        <v>16000</v>
       </c>
       <c r="O4" s="1">
-        <v>16000.0</v>
-      </c>
-      <c r="P4" s="1">
-        <v>14000.0</v>
-      </c>
-      <c r="Q4" s="1">
-        <v>12000.0</v>
-      </c>
+        <v>14000</v>
+      </c>
+      <c r="P4" s="1"/>
+      <c r="Q4" s="1"/>
       <c r="R4" s="1">
-        <v>14000.0</v>
+        <v>12000</v>
       </c>
       <c r="S4" s="1">
-        <v>16000.0</v>
+        <v>14000</v>
       </c>
       <c r="T4" s="1">
-        <v>14000.0</v>
+        <v>16000</v>
       </c>
       <c r="U4" s="1">
-        <v>12000.0</v>
+        <v>14000</v>
       </c>
       <c r="V4" s="1">
-        <v>14000.0</v>
+        <v>12000</v>
       </c>
       <c r="W4" s="1">
-        <v>16000.0</v>
+        <v>14000</v>
       </c>
       <c r="X4" s="1">
-        <v>14000.0</v>
+        <v>16000</v>
       </c>
       <c r="Y4" s="1">
-        <v>12000.0</v>
+        <v>14000</v>
       </c>
       <c r="Z4" s="1">
-        <v>14000.0</v>
+        <v>12000</v>
       </c>
       <c r="AA4" s="1">
-        <v>16000.0</v>
+        <v>14000</v>
       </c>
       <c r="AB4" s="1">
-        <v>14000.0</v>
-      </c>
-    </row>
-    <row r="5" ht="14.0">
+        <v>16000</v>
+      </c>
+      <c r="AC4" s="1">
+        <v>14000</v>
+      </c>
+      <c r="AD4" s="1">
+        <v>12000</v>
+      </c>
+      <c r="AE4" s="1">
+        <v>14000</v>
+      </c>
+      <c r="AF4" s="1">
+        <v>16000</v>
+      </c>
+      <c r="AG4" s="1">
+        <v>14000</v>
+      </c>
+    </row>
+    <row r="5" spans="1:33" ht="12.75" x14ac:dyDescent="0.2">
       <c r="H5" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="I5" s="1">
-        <v>18000.0</v>
-      </c>
-      <c r="J5" s="1">
-        <v>20000.0</v>
-      </c>
-      <c r="K5" s="1">
-        <v>22000.0</v>
-      </c>
+      <c r="I5" s="1"/>
+      <c r="J5" s="1"/>
       <c r="L5" s="1">
-        <v>20000.0</v>
+        <v>18000</v>
       </c>
       <c r="M5" s="1">
-        <v>18000.0</v>
+        <v>20000</v>
       </c>
       <c r="N5" s="1">
-        <v>20000.0</v>
+        <v>22000</v>
       </c>
       <c r="O5" s="1">
-        <v>22000.0</v>
-      </c>
-      <c r="P5" s="1">
-        <v>20000.0</v>
-      </c>
-      <c r="Q5" s="1">
-        <v>18000.0</v>
-      </c>
+        <v>20000</v>
+      </c>
+      <c r="P5" s="1"/>
+      <c r="Q5" s="1"/>
       <c r="R5" s="1">
-        <v>20000.0</v>
+        <v>18000</v>
       </c>
       <c r="S5" s="1">
-        <v>22000.0</v>
+        <v>20000</v>
       </c>
       <c r="T5" s="1">
-        <v>20000.0</v>
+        <v>22000</v>
       </c>
       <c r="U5" s="1">
-        <v>18000.0</v>
+        <v>20000</v>
       </c>
       <c r="V5" s="1">
-        <v>20000.0</v>
+        <v>18000</v>
       </c>
       <c r="W5" s="1">
-        <v>22000.0</v>
+        <v>20000</v>
       </c>
       <c r="X5" s="1">
-        <v>20000.0</v>
+        <v>22000</v>
       </c>
       <c r="Y5" s="1">
-        <v>18000.0</v>
+        <v>20000</v>
       </c>
       <c r="Z5" s="1">
-        <v>20000.0</v>
+        <v>18000</v>
       </c>
       <c r="AA5" s="1">
-        <v>22000.0</v>
+        <v>20000</v>
       </c>
       <c r="AB5" s="1">
-        <v>20000.0</v>
-      </c>
-    </row>
-    <row r="6" ht="14.0">
+        <v>22000</v>
+      </c>
+      <c r="AC5" s="1">
+        <v>20000</v>
+      </c>
+      <c r="AD5" s="1">
+        <v>18000</v>
+      </c>
+      <c r="AE5" s="1">
+        <v>20000</v>
+      </c>
+      <c r="AF5" s="1">
+        <v>22000</v>
+      </c>
+      <c r="AG5" s="1">
+        <v>20000</v>
+      </c>
+    </row>
+    <row r="6" spans="1:33" ht="12.75" x14ac:dyDescent="0.2">
       <c r="H6" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="I6" s="1">
-        <v>3000.0</v>
-      </c>
-      <c r="J6" s="1">
-        <v>4500.0</v>
-      </c>
-      <c r="K6" s="1">
-        <v>5500.0</v>
-      </c>
+      <c r="I6" s="1"/>
+      <c r="J6" s="1"/>
       <c r="L6" s="1">
-        <v>4500.0</v>
+        <v>3000</v>
       </c>
       <c r="M6" s="1">
-        <v>3000.0</v>
+        <v>4500</v>
       </c>
       <c r="N6" s="1">
-        <v>4500.0</v>
+        <v>5500</v>
       </c>
       <c r="O6" s="1">
-        <v>5500.0</v>
-      </c>
-      <c r="P6" s="1">
-        <v>4500.0</v>
-      </c>
-      <c r="Q6" s="1">
-        <v>3000.0</v>
-      </c>
+        <v>4500</v>
+      </c>
+      <c r="P6" s="1"/>
+      <c r="Q6" s="1"/>
       <c r="R6" s="1">
-        <v>4500.0</v>
+        <v>3000</v>
       </c>
       <c r="S6" s="1">
-        <v>5500.0</v>
+        <v>4500</v>
       </c>
       <c r="T6" s="1">
-        <v>4500.0</v>
+        <v>5500</v>
       </c>
       <c r="U6" s="1">
-        <v>3000.0</v>
+        <v>4500</v>
       </c>
       <c r="V6" s="1">
-        <v>4500.0</v>
+        <v>3000</v>
       </c>
       <c r="W6" s="1">
-        <v>5500.0</v>
+        <v>4500</v>
       </c>
       <c r="X6" s="1">
-        <v>4500.0</v>
+        <v>5500</v>
       </c>
       <c r="Y6" s="1">
-        <v>3000.0</v>
+        <v>4500</v>
       </c>
       <c r="Z6" s="1">
-        <v>4500.0</v>
+        <v>3000</v>
       </c>
       <c r="AA6" s="1">
-        <v>5500.0</v>
+        <v>4500</v>
       </c>
       <c r="AB6" s="1">
-        <v>4500.0</v>
-      </c>
-    </row>
-    <row r="7" ht="14.0">
+        <v>5500</v>
+      </c>
+      <c r="AC6" s="1">
+        <v>4500</v>
+      </c>
+      <c r="AD6" s="1">
+        <v>3000</v>
+      </c>
+      <c r="AE6" s="1">
+        <v>4500</v>
+      </c>
+      <c r="AF6" s="1">
+        <v>5500</v>
+      </c>
+      <c r="AG6" s="1">
+        <v>4500</v>
+      </c>
+    </row>
+    <row r="7" spans="1:33" ht="12.75" x14ac:dyDescent="0.2">
       <c r="H7" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="I7" s="1">
-        <v>2000.0</v>
-      </c>
-      <c r="J7" s="1">
-        <v>3500.0</v>
-      </c>
-      <c r="K7" s="1">
-        <v>4500.0</v>
-      </c>
+      <c r="I7" s="1"/>
+      <c r="J7" s="1"/>
       <c r="L7" s="1">
-        <v>3500.0</v>
+        <v>2000</v>
       </c>
       <c r="M7" s="1">
-        <v>2000.0</v>
+        <v>3500</v>
       </c>
       <c r="N7" s="1">
-        <v>3500.0</v>
+        <v>4500</v>
       </c>
       <c r="O7" s="1">
-        <v>4500.0</v>
-      </c>
-      <c r="P7" s="1">
-        <v>3500.0</v>
-      </c>
-      <c r="Q7" s="1">
-        <v>2000.0</v>
-      </c>
+        <v>3500</v>
+      </c>
+      <c r="P7" s="1"/>
+      <c r="Q7" s="1"/>
       <c r="R7" s="1">
-        <v>3500.0</v>
+        <v>2000</v>
       </c>
       <c r="S7" s="1">
-        <v>4500.0</v>
+        <v>3500</v>
       </c>
       <c r="T7" s="1">
-        <v>3500.0</v>
+        <v>4500</v>
       </c>
       <c r="U7" s="1">
-        <v>2000.0</v>
+        <v>3500</v>
       </c>
       <c r="V7" s="1">
-        <v>3500.0</v>
+        <v>2000</v>
       </c>
       <c r="W7" s="1">
-        <v>4500.0</v>
+        <v>3500</v>
       </c>
       <c r="X7" s="1">
-        <v>3500.0</v>
+        <v>4500</v>
       </c>
       <c r="Y7" s="1">
-        <v>2000.0</v>
+        <v>3500</v>
       </c>
       <c r="Z7" s="1">
-        <v>3500.0</v>
+        <v>2000</v>
       </c>
       <c r="AA7" s="1">
-        <v>4500.0</v>
+        <v>3500</v>
       </c>
       <c r="AB7" s="1">
-        <v>3500.0</v>
-      </c>
-    </row>
-    <row r="8" ht="14.0">
+        <v>4500</v>
+      </c>
+      <c r="AC7" s="1">
+        <v>3500</v>
+      </c>
+      <c r="AD7" s="1">
+        <v>2000</v>
+      </c>
+      <c r="AE7" s="1">
+        <v>3500</v>
+      </c>
+      <c r="AF7" s="1">
+        <v>4500</v>
+      </c>
+      <c r="AG7" s="1">
+        <v>3500</v>
+      </c>
+    </row>
+    <row r="8" spans="1:33" ht="12.75" x14ac:dyDescent="0.2">
       <c r="H8" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="I8" s="1">
-        <v>1000.0</v>
-      </c>
-      <c r="J8" s="1">
-        <v>2500.0</v>
-      </c>
-      <c r="K8" s="1">
-        <v>3500.0</v>
-      </c>
+      <c r="I8" s="1"/>
+      <c r="J8" s="1"/>
       <c r="L8" s="1">
-        <v>2500.0</v>
+        <v>1000</v>
       </c>
       <c r="M8" s="1">
-        <v>1000.0</v>
+        <v>2500</v>
       </c>
       <c r="N8" s="1">
-        <v>2500.0</v>
+        <v>3500</v>
       </c>
       <c r="O8" s="1">
-        <v>3500.0</v>
-      </c>
-      <c r="P8" s="1">
-        <v>2500.0</v>
-      </c>
-      <c r="Q8" s="1">
-        <v>1000.0</v>
-      </c>
+        <v>2500</v>
+      </c>
+      <c r="P8" s="1"/>
+      <c r="Q8" s="1"/>
       <c r="R8" s="1">
-        <v>2500.0</v>
+        <v>1000</v>
       </c>
       <c r="S8" s="1">
-        <v>3500.0</v>
+        <v>2500</v>
       </c>
       <c r="T8" s="1">
-        <v>2500.0</v>
+        <v>3500</v>
       </c>
       <c r="U8" s="1">
-        <v>1000.0</v>
+        <v>2500</v>
       </c>
       <c r="V8" s="1">
-        <v>2500.0</v>
+        <v>1000</v>
       </c>
       <c r="W8" s="1">
-        <v>3500.0</v>
+        <v>2500</v>
       </c>
       <c r="X8" s="1">
-        <v>2500.0</v>
+        <v>3500</v>
       </c>
       <c r="Y8" s="1">
-        <v>1000.0</v>
+        <v>2500</v>
       </c>
       <c r="Z8" s="1">
-        <v>2500.0</v>
+        <v>1000</v>
       </c>
       <c r="AA8" s="1">
-        <v>3500.0</v>
+        <v>2500</v>
       </c>
       <c r="AB8" s="1">
-        <v>2500.0</v>
-      </c>
-    </row>
-    <row r="9" ht="14.0">
+        <v>3500</v>
+      </c>
+      <c r="AC8" s="1">
+        <v>2500</v>
+      </c>
+      <c r="AD8" s="1">
+        <v>1000</v>
+      </c>
+      <c r="AE8" s="1">
+        <v>2500</v>
+      </c>
+      <c r="AF8" s="1">
+        <v>3500</v>
+      </c>
+      <c r="AG8" s="1">
+        <v>2500</v>
+      </c>
+    </row>
+    <row r="9" spans="1:33" ht="12.75" x14ac:dyDescent="0.2">
       <c r="B9" s="1" t="s">
         <v>30</v>
       </c>
@@ -775,7 +1094,7 @@
         <v>33</v>
       </c>
       <c r="G9" s="1">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="H9" s="1"/>
       <c r="I9" s="1" t="s">
@@ -788,138 +1107,167 @@
         <v>46387</v>
       </c>
       <c r="L9" s="1"/>
-      <c r="M9" s="1"/>
+      <c r="M9" s="3"/>
       <c r="N9" s="1"/>
       <c r="O9" s="1"/>
       <c r="P9" s="1"/>
       <c r="Q9" s="1"/>
-    </row>
-    <row r="10" ht="14.0">
+      <c r="R9" s="1"/>
+      <c r="S9" s="1"/>
+      <c r="T9" s="1"/>
+      <c r="U9" s="1"/>
+      <c r="V9" s="1"/>
+    </row>
+    <row r="10" spans="1:33" ht="12.75" x14ac:dyDescent="0.2">
       <c r="A10" s="1"/>
       <c r="H10" s="1"/>
-      <c r="I10" s="1" t="s">
+      <c r="I10" s="1"/>
+      <c r="J10" s="1"/>
+      <c r="L10" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="J10" s="1" t="s">
+      <c r="M10" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="K10" s="1" t="s">
+      <c r="N10" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="L10" s="1" t="s">
+      <c r="O10" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="M10" s="1"/>
-      <c r="N10" s="1"/>
-      <c r="O10" s="1"/>
       <c r="P10" s="1"/>
-    </row>
-    <row r="11" ht="14.0">
+      <c r="Q10" s="1"/>
+      <c r="R10" s="1"/>
+      <c r="S10" s="1"/>
+      <c r="T10" s="1"/>
+      <c r="U10" s="1"/>
+    </row>
+    <row r="11" spans="1:33" ht="12.75" x14ac:dyDescent="0.2">
       <c r="H11" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="I11" s="1">
-        <v>8500.0</v>
-      </c>
-      <c r="J11" s="1">
-        <v>10000.0</v>
-      </c>
-      <c r="K11" s="1">
-        <v>12000.0</v>
-      </c>
+      <c r="I11" s="1"/>
+      <c r="J11" s="1"/>
       <c r="L11" s="1">
-        <v>10000.0</v>
-      </c>
-      <c r="M11" s="1"/>
-      <c r="N11" s="1"/>
-      <c r="O11" s="1"/>
+        <v>8500</v>
+      </c>
+      <c r="M11" s="1">
+        <v>10000</v>
+      </c>
+      <c r="N11" s="1">
+        <v>12000</v>
+      </c>
+      <c r="O11" s="1">
+        <v>10000</v>
+      </c>
       <c r="P11" s="1"/>
-    </row>
-    <row r="12" ht="14.0">
+      <c r="Q11" s="1"/>
+      <c r="R11" s="1"/>
+      <c r="S11" s="1"/>
+      <c r="T11" s="1"/>
+      <c r="U11" s="1"/>
+    </row>
+    <row r="12" spans="1:33" ht="12.75" x14ac:dyDescent="0.2">
       <c r="H12" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="I12" s="1">
-        <v>15000.0</v>
-      </c>
-      <c r="J12" s="1">
-        <v>17000.0</v>
-      </c>
-      <c r="K12" s="1">
-        <v>19000.0</v>
-      </c>
+      <c r="I12" s="1"/>
+      <c r="J12" s="1"/>
       <c r="L12" s="1">
-        <v>17000.0</v>
-      </c>
-      <c r="M12" s="1"/>
-      <c r="N12" s="1"/>
-      <c r="O12" s="1"/>
+        <v>15000</v>
+      </c>
+      <c r="M12" s="1">
+        <v>17000</v>
+      </c>
+      <c r="N12" s="1">
+        <v>19000</v>
+      </c>
+      <c r="O12" s="1">
+        <v>17000</v>
+      </c>
       <c r="P12" s="1"/>
-    </row>
-    <row r="13" ht="14.0">
+      <c r="Q12" s="1"/>
+      <c r="R12" s="1"/>
+      <c r="S12" s="1"/>
+      <c r="T12" s="1"/>
+      <c r="U12" s="1"/>
+    </row>
+    <row r="13" spans="1:33" ht="12.75" x14ac:dyDescent="0.2">
       <c r="H13" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="I13" s="1">
-        <v>2500.0</v>
-      </c>
-      <c r="J13" s="1">
-        <v>3500.0</v>
-      </c>
-      <c r="K13" s="1">
-        <v>4500.0</v>
-      </c>
+      <c r="I13" s="1"/>
+      <c r="J13" s="1"/>
       <c r="L13" s="1">
-        <v>3500.0</v>
-      </c>
-      <c r="M13" s="1"/>
-      <c r="N13" s="1"/>
-      <c r="O13" s="1"/>
+        <v>2500</v>
+      </c>
+      <c r="M13" s="1">
+        <v>3500</v>
+      </c>
+      <c r="N13" s="1">
+        <v>4500</v>
+      </c>
+      <c r="O13" s="1">
+        <v>3500</v>
+      </c>
       <c r="P13" s="1"/>
-    </row>
-    <row r="14" ht="14.0">
+      <c r="Q13" s="1"/>
+      <c r="R13" s="1"/>
+      <c r="S13" s="1"/>
+      <c r="T13" s="1"/>
+      <c r="U13" s="1"/>
+    </row>
+    <row r="14" spans="1:33" ht="12.75" x14ac:dyDescent="0.2">
       <c r="H14" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="I14" s="1">
-        <v>1500.0</v>
-      </c>
-      <c r="J14" s="1">
-        <v>2500.0</v>
-      </c>
-      <c r="K14" s="1">
-        <v>3500.0</v>
-      </c>
+      <c r="I14" s="1"/>
+      <c r="J14" s="1"/>
       <c r="L14" s="1">
-        <v>2500.0</v>
-      </c>
-      <c r="M14" s="1"/>
-      <c r="N14" s="1"/>
-      <c r="O14" s="1"/>
+        <v>1500</v>
+      </c>
+      <c r="M14" s="1">
+        <v>2500</v>
+      </c>
+      <c r="N14" s="1">
+        <v>3500</v>
+      </c>
+      <c r="O14" s="1">
+        <v>2500</v>
+      </c>
       <c r="P14" s="1"/>
-    </row>
-    <row r="15" customHeight="1" ht="16.0">
+      <c r="Q14" s="1"/>
+      <c r="R14" s="1"/>
+      <c r="S14" s="1"/>
+      <c r="T14" s="1"/>
+      <c r="U14" s="1"/>
+    </row>
+    <row r="15" spans="1:33" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="H15" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="I15" s="1">
-        <v>800.0</v>
-      </c>
-      <c r="J15" s="1">
-        <v>1800.0</v>
-      </c>
-      <c r="K15" s="1">
-        <v>2800.0</v>
-      </c>
+      <c r="I15" s="1"/>
+      <c r="J15" s="1"/>
       <c r="L15" s="1">
-        <v>1800.0</v>
-      </c>
-      <c r="M15" s="1"/>
-      <c r="N15" s="1"/>
-      <c r="O15" s="1"/>
+        <v>800</v>
+      </c>
+      <c r="M15" s="1">
+        <v>1800</v>
+      </c>
+      <c r="N15" s="1">
+        <v>2800</v>
+      </c>
+      <c r="O15" s="1">
+        <v>1800</v>
+      </c>
       <c r="P15" s="1"/>
-    </row>
-    <row r="16" customHeight="1" ht="16.0">
+      <c r="Q15" s="1"/>
+      <c r="R15" s="1"/>
+      <c r="S15" s="1"/>
+      <c r="T15" s="1"/>
+      <c r="U15" s="1"/>
+    </row>
+    <row r="16" spans="1:33" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B16" s="1" t="s">
         <v>37</v>
       </c>
@@ -930,405 +1278,434 @@
         <v>39</v>
       </c>
       <c r="E16" s="1">
-        <v>4.9</v>
+        <v>4.9000000000000004</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>13</v>
       </c>
       <c r="G16" s="1">
-        <v>3.0</v>
-      </c>
-      <c r="I16" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="I16" t="s">
         <v>14</v>
       </c>
-      <c r="J16" s="4">
-        <v>46023.0</v>
-      </c>
-      <c r="K16" s="1" t="s">
+      <c r="K16" s="1"/>
+      <c r="L16" s="4">
+        <v>46023</v>
+      </c>
+      <c r="M16" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="M16" s="1" t="s">
+      <c r="R16" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="N16" s="4">
-        <v>46083.0</v>
-      </c>
-      <c r="O16" s="3">
+      <c r="S16" s="4">
+        <v>46083</v>
+      </c>
+      <c r="T16" s="3">
         <v>46143</v>
       </c>
-      <c r="Q16" s="1" t="s">
+      <c r="V16" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="R16" s="4">
-        <v>46144.0</v>
-      </c>
-      <c r="S16" s="1" t="s">
+      <c r="W16" s="4">
+        <v>46144</v>
+      </c>
+      <c r="X16" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="U16" s="1" t="s">
+      <c r="Z16" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="V16" s="4">
-        <v>46242.0</v>
-      </c>
-      <c r="W16" s="3">
+      <c r="AA16" s="4">
+        <v>46242</v>
+      </c>
+      <c r="AB16" s="3">
         <v>46265</v>
       </c>
-      <c r="Z16" s="1"/>
-      <c r="AA16" s="4"/>
-      <c r="AB16" s="3"/>
-    </row>
-    <row r="17" customHeight="1" ht="16.0">
-      <c r="I17" s="1" t="s">
+      <c r="AE16" s="1"/>
+      <c r="AF16" s="4"/>
+      <c r="AG16" s="3"/>
+    </row>
+    <row r="17" spans="8:34" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="K17" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="J17" s="1" t="s">
+      <c r="L17" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="K17" s="1" t="s">
+      <c r="M17" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="L17" s="1" t="s">
+      <c r="N17" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="M17" s="1" t="s">
+      <c r="O17" s="1"/>
+      <c r="P17" s="1"/>
+      <c r="Q17" s="1"/>
+      <c r="R17" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="N17" s="1" t="s">
+      <c r="S17" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="O17" s="1" t="s">
+      <c r="T17" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="P17" s="1" t="s">
+      <c r="U17" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="Q17" s="1" t="s">
+      <c r="V17" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="R17" s="1" t="s">
+      <c r="W17" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="S17" s="1" t="s">
+      <c r="X17" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="T17" s="1" t="s">
+      <c r="Y17" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="U17" s="1" t="s">
+      <c r="Z17" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="V17" s="1" t="s">
+      <c r="AA17" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="W17" s="1" t="s">
+      <c r="AB17" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="X17" s="1" t="s">
+      <c r="AC17" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="Y17" s="1"/>
-      <c r="Z17" s="1"/>
-      <c r="AA17" s="1"/>
-      <c r="AB17" s="1"/>
-      <c r="AC17" s="1"/>
-    </row>
-    <row r="18" customHeight="1" ht="16.0">
+      <c r="AD17" s="1"/>
+      <c r="AE17" s="1"/>
+      <c r="AF17" s="1"/>
+      <c r="AG17" s="1"/>
+      <c r="AH17" s="1"/>
+    </row>
+    <row r="18" spans="8:34" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="H18" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="I18" s="1">
-        <v>12000.0</v>
-      </c>
-      <c r="J18" s="1">
-        <v>14000.0</v>
-      </c>
+      <c r="I18" s="1"/>
+      <c r="J18" s="1"/>
       <c r="K18" s="1">
-        <v>16000.0</v>
+        <v>12000</v>
       </c>
       <c r="L18" s="1">
-        <v>14000.0</v>
+        <v>14000</v>
       </c>
       <c r="M18" s="1">
-        <v>12000.0</v>
+        <v>16000</v>
       </c>
       <c r="N18" s="1">
-        <v>14000.0</v>
-      </c>
-      <c r="O18" s="1">
-        <v>16000.0</v>
-      </c>
-      <c r="P18" s="1">
-        <v>14000.0</v>
-      </c>
-      <c r="Q18" s="1">
-        <v>12000.0</v>
-      </c>
+        <v>14000</v>
+      </c>
+      <c r="O18" s="1"/>
+      <c r="P18" s="1"/>
+      <c r="Q18" s="1"/>
       <c r="R18" s="1">
-        <v>14000.0</v>
+        <v>12000</v>
       </c>
       <c r="S18" s="1">
-        <v>16000.0</v>
+        <v>14000</v>
       </c>
       <c r="T18" s="1">
-        <v>14000.0</v>
+        <v>16000</v>
       </c>
       <c r="U18" s="1">
-        <v>12000.0</v>
+        <v>14000</v>
       </c>
       <c r="V18" s="1">
-        <v>14000.0</v>
+        <v>12000</v>
       </c>
       <c r="W18" s="1">
-        <v>16000.0</v>
+        <v>14000</v>
       </c>
       <c r="X18" s="1">
-        <v>14000.0</v>
-      </c>
-      <c r="Y18" s="1"/>
-      <c r="Z18" s="1"/>
-      <c r="AA18" s="1"/>
-      <c r="AB18" s="1"/>
-      <c r="AC18" s="1"/>
-    </row>
-    <row r="19" customHeight="1" ht="16.0">
+        <v>16000</v>
+      </c>
+      <c r="Y18" s="1">
+        <v>14000</v>
+      </c>
+      <c r="Z18" s="1">
+        <v>12000</v>
+      </c>
+      <c r="AA18" s="1">
+        <v>14000</v>
+      </c>
+      <c r="AB18" s="1">
+        <v>16000</v>
+      </c>
+      <c r="AC18" s="1">
+        <v>14000</v>
+      </c>
+      <c r="AD18" s="1"/>
+      <c r="AE18" s="1"/>
+      <c r="AF18" s="1"/>
+      <c r="AG18" s="1"/>
+      <c r="AH18" s="1"/>
+    </row>
+    <row r="19" spans="8:34" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="H19" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="I19" s="1">
-        <v>18000.0</v>
-      </c>
-      <c r="J19" s="1">
-        <v>20000.0</v>
-      </c>
+      <c r="I19" s="1"/>
+      <c r="J19" s="1"/>
       <c r="K19" s="1">
-        <v>22000.0</v>
+        <v>18000</v>
       </c>
       <c r="L19" s="1">
-        <v>20000.0</v>
+        <v>20000</v>
       </c>
       <c r="M19" s="1">
-        <v>18000.0</v>
+        <v>22000</v>
       </c>
       <c r="N19" s="1">
-        <v>20000.0</v>
-      </c>
-      <c r="O19" s="1">
-        <v>22000.0</v>
-      </c>
-      <c r="P19" s="1">
-        <v>20000.0</v>
-      </c>
-      <c r="Q19" s="1">
-        <v>18000.0</v>
-      </c>
+        <v>20000</v>
+      </c>
+      <c r="O19" s="1"/>
+      <c r="P19" s="1"/>
+      <c r="Q19" s="1"/>
       <c r="R19" s="1">
-        <v>20000.0</v>
+        <v>18000</v>
       </c>
       <c r="S19" s="1">
-        <v>22000.0</v>
+        <v>20000</v>
       </c>
       <c r="T19" s="1">
-        <v>20000.0</v>
+        <v>22000</v>
       </c>
       <c r="U19" s="1">
-        <v>18000.0</v>
+        <v>20000</v>
       </c>
       <c r="V19" s="1">
-        <v>20000.0</v>
+        <v>18000</v>
       </c>
       <c r="W19" s="1">
-        <v>22000.0</v>
+        <v>20000</v>
       </c>
       <c r="X19" s="1">
-        <v>20000.0</v>
-      </c>
-      <c r="Y19" s="1"/>
-      <c r="Z19" s="1"/>
-      <c r="AA19" s="1"/>
-      <c r="AB19" s="1"/>
-      <c r="AC19" s="1"/>
-    </row>
-    <row r="20" customHeight="1" ht="16.0">
+        <v>22000</v>
+      </c>
+      <c r="Y19" s="1">
+        <v>20000</v>
+      </c>
+      <c r="Z19" s="1">
+        <v>18000</v>
+      </c>
+      <c r="AA19" s="1">
+        <v>20000</v>
+      </c>
+      <c r="AB19" s="1">
+        <v>22000</v>
+      </c>
+      <c r="AC19" s="1">
+        <v>20000</v>
+      </c>
+      <c r="AD19" s="1"/>
+      <c r="AE19" s="1"/>
+      <c r="AF19" s="1"/>
+      <c r="AG19" s="1"/>
+      <c r="AH19" s="1"/>
+    </row>
+    <row r="20" spans="8:34" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="H20" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="I20" s="1">
-        <v>3000.0</v>
-      </c>
-      <c r="J20" s="1">
-        <v>4500.0</v>
-      </c>
+      <c r="I20" s="1"/>
+      <c r="J20" s="1"/>
       <c r="K20" s="1">
-        <v>5500.0</v>
+        <v>3000</v>
       </c>
       <c r="L20" s="1">
-        <v>4500.0</v>
+        <v>4500</v>
       </c>
       <c r="M20" s="1">
-        <v>3000.0</v>
+        <v>5500</v>
       </c>
       <c r="N20" s="1">
-        <v>4500.0</v>
-      </c>
-      <c r="O20" s="1">
-        <v>5500.0</v>
-      </c>
-      <c r="P20" s="1">
-        <v>4500.0</v>
-      </c>
-      <c r="Q20" s="1">
-        <v>3000.0</v>
-      </c>
+        <v>4500</v>
+      </c>
+      <c r="O20" s="1"/>
+      <c r="P20" s="1"/>
+      <c r="Q20" s="1"/>
       <c r="R20" s="1">
-        <v>4500.0</v>
+        <v>3000</v>
       </c>
       <c r="S20" s="1">
-        <v>5500.0</v>
+        <v>4500</v>
       </c>
       <c r="T20" s="1">
-        <v>4500.0</v>
+        <v>5500</v>
       </c>
       <c r="U20" s="1">
-        <v>3000.0</v>
+        <v>4500</v>
       </c>
       <c r="V20" s="1">
-        <v>4500.0</v>
+        <v>3000</v>
       </c>
       <c r="W20" s="1">
-        <v>5500.0</v>
+        <v>4500</v>
       </c>
       <c r="X20" s="1">
-        <v>4500.0</v>
-      </c>
-      <c r="Y20" s="1"/>
-      <c r="Z20" s="1"/>
-      <c r="AA20" s="1"/>
-      <c r="AB20" s="1"/>
-      <c r="AC20" s="1"/>
-    </row>
-    <row r="21" customHeight="1" ht="16.0">
+        <v>5500</v>
+      </c>
+      <c r="Y20" s="1">
+        <v>4500</v>
+      </c>
+      <c r="Z20" s="1">
+        <v>3000</v>
+      </c>
+      <c r="AA20" s="1">
+        <v>4500</v>
+      </c>
+      <c r="AB20" s="1">
+        <v>5500</v>
+      </c>
+      <c r="AC20" s="1">
+        <v>4500</v>
+      </c>
+      <c r="AD20" s="1"/>
+      <c r="AE20" s="1"/>
+      <c r="AF20" s="1"/>
+      <c r="AG20" s="1"/>
+      <c r="AH20" s="1"/>
+    </row>
+    <row r="21" spans="8:34" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="H21" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="I21" s="1">
-        <v>2000.0</v>
-      </c>
-      <c r="J21" s="1">
-        <v>3500.0</v>
-      </c>
+      <c r="I21" s="1"/>
+      <c r="J21" s="1"/>
       <c r="K21" s="1">
-        <v>4500.0</v>
+        <v>2000</v>
       </c>
       <c r="L21" s="1">
-        <v>3500.0</v>
+        <v>3500</v>
       </c>
       <c r="M21" s="1">
-        <v>2000.0</v>
+        <v>4500</v>
       </c>
       <c r="N21" s="1">
-        <v>3500.0</v>
-      </c>
-      <c r="O21" s="1">
-        <v>4500.0</v>
-      </c>
-      <c r="P21" s="1">
-        <v>3500.0</v>
-      </c>
-      <c r="Q21" s="1">
-        <v>2000.0</v>
-      </c>
+        <v>3500</v>
+      </c>
+      <c r="O21" s="1"/>
+      <c r="P21" s="1"/>
+      <c r="Q21" s="1"/>
       <c r="R21" s="1">
-        <v>3500.0</v>
+        <v>2000</v>
       </c>
       <c r="S21" s="1">
-        <v>4500.0</v>
+        <v>3500</v>
       </c>
       <c r="T21" s="1">
-        <v>3500.0</v>
+        <v>4500</v>
       </c>
       <c r="U21" s="1">
-        <v>2000.0</v>
+        <v>3500</v>
       </c>
       <c r="V21" s="1">
-        <v>3500.0</v>
+        <v>2000</v>
       </c>
       <c r="W21" s="1">
-        <v>4500.0</v>
+        <v>3500</v>
       </c>
       <c r="X21" s="1">
-        <v>3500.0</v>
-      </c>
-      <c r="Y21" s="1"/>
-      <c r="Z21" s="1"/>
-      <c r="AA21" s="1"/>
-      <c r="AB21" s="1"/>
-      <c r="AC21" s="1"/>
-    </row>
-    <row r="22" customHeight="1" ht="16.0">
+        <v>4500</v>
+      </c>
+      <c r="Y21" s="1">
+        <v>3500</v>
+      </c>
+      <c r="Z21" s="1">
+        <v>2000</v>
+      </c>
+      <c r="AA21" s="1">
+        <v>3500</v>
+      </c>
+      <c r="AB21" s="1">
+        <v>4500</v>
+      </c>
+      <c r="AC21" s="1">
+        <v>3500</v>
+      </c>
+      <c r="AD21" s="1"/>
+      <c r="AE21" s="1"/>
+      <c r="AF21" s="1"/>
+      <c r="AG21" s="1"/>
+      <c r="AH21" s="1"/>
+    </row>
+    <row r="22" spans="8:34" ht="15.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="H22" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="I22" s="1">
-        <v>1000.0</v>
-      </c>
-      <c r="J22" s="1">
-        <v>2500.0</v>
-      </c>
+      <c r="I22" s="1"/>
+      <c r="J22" s="1"/>
       <c r="K22" s="1">
-        <v>3500.0</v>
+        <v>1000</v>
       </c>
       <c r="L22" s="1">
-        <v>2500.0</v>
+        <v>2500</v>
       </c>
       <c r="M22" s="1">
-        <v>1000.0</v>
+        <v>3500</v>
       </c>
       <c r="N22" s="1">
-        <v>2500.0</v>
-      </c>
-      <c r="O22" s="1">
-        <v>3500.0</v>
-      </c>
-      <c r="P22" s="1">
-        <v>2500.0</v>
-      </c>
-      <c r="Q22" s="1">
-        <v>1000.0</v>
-      </c>
+        <v>2500</v>
+      </c>
+      <c r="O22" s="1"/>
+      <c r="P22" s="1"/>
+      <c r="Q22" s="1"/>
       <c r="R22" s="1">
-        <v>2500.0</v>
+        <v>1000</v>
       </c>
       <c r="S22" s="1">
-        <v>3500.0</v>
+        <v>2500</v>
       </c>
       <c r="T22" s="1">
-        <v>2500.0</v>
+        <v>3500</v>
       </c>
       <c r="U22" s="1">
-        <v>1000.0</v>
+        <v>2500</v>
       </c>
       <c r="V22" s="1">
-        <v>2500.0</v>
+        <v>1000</v>
       </c>
       <c r="W22" s="1">
-        <v>3500.0</v>
+        <v>2500</v>
       </c>
       <c r="X22" s="1">
-        <v>2500.0</v>
-      </c>
-      <c r="Y22" s="1"/>
-      <c r="Z22" s="1"/>
-      <c r="AA22" s="1"/>
-      <c r="AB22" s="1"/>
-      <c r="AC22" s="1"/>
+        <v>3500</v>
+      </c>
+      <c r="Y22" s="1">
+        <v>2500</v>
+      </c>
+      <c r="Z22" s="1">
+        <v>1000</v>
+      </c>
+      <c r="AA22" s="1">
+        <v>2500</v>
+      </c>
+      <c r="AB22" s="1">
+        <v>3500</v>
+      </c>
+      <c r="AC22" s="1">
+        <v>2500</v>
+      </c>
+      <c r="AD22" s="1"/>
+      <c r="AE22" s="1"/>
+      <c r="AF22" s="1"/>
+      <c r="AG22" s="1"/>
+      <c r="AH22" s="1"/>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="F2" r:id="rId1"/>
-    <hyperlink ref="F9" r:id="rId2"/>
-    <hyperlink ref="F16" r:id="rId3"/>
+    <hyperlink ref="F2" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
+    <hyperlink ref="F9" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
+    <hyperlink ref="F16" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
   </hyperlinks>
-  <extLst/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>